--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>128185300</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,7 +869,11 @@
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185300</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>8442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185300</v>
       </c>
       <c r="B3" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36366-2025 artfynd.xlsx
+++ b/artfynd/A 36366-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185302</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
